--- a/resultados/antonina/erros_varredura.xlsx
+++ b/resultados/antonina/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
+          <t>https://www.antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30 18:03:34</t>
+          <t>2026-08-03 02:00:29</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>http://antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
+          <t>https://www.antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -496,11 +496,11 @@
         <v>404</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30 18:05:59</t>
+          <t>2026-08-03 02:00:45</t>
         </is>
       </c>
     </row>
@@ -512,23 +512,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/noticiasView/9</t>
+          <t>https://www.antonina.pr.gov.br/turismo/?categoria=1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-30 18:56:56</t>
+          <t>2026-08-03 02:01:39</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/.../CHAMAMENTO-ELEICAO?fbclid=IwAR0eXNjpoLZiJ7kZYK9Ul8OJ11SelP78G2bzg5VAIIJxXN761txEOnUS8R8</t>
+          <t>http://antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -552,11 +552,11 @@
         <v>404</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-30 18:57:04</t>
+          <t>2026-08-03 02:02:35</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/noticiasView/e</t>
+          <t>http://antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -580,11 +580,11 @@
         <v>404</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30 18:57:12</t>
+          <t>2026-08-03 02:02:39</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>http://www.antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
+          <t>https://antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,11 +608,11 @@
         <v>404</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-30 18:57:54</t>
+          <t>2026-08-03 02:08:17</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>http://antonina.pr.gov.br/noticiasView/9</t>
+          <t>https://antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -636,11 +636,11 @@
         <v>404</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30 19:12:49</t>
+          <t>2026-08-03 02:08:30</t>
         </is>
       </c>
     </row>
@@ -652,23 +652,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>http://antonina.pr.gov.br/noticiasView/e</t>
+          <t>http://antonina.pr.gov.br/turismo/?categoria=1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30 19:12:57</t>
+          <t>2026-08-03 02:09:14</t>
         </is>
       </c>
     </row>
@@ -680,23 +680,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/uploads/pagina/arquivos/PSS-003-2025-1-1?fbclid=IwZXh0bgNhZW0CMTAAYnJpZBExNURYa1VZWllVY1k5SzFFMQEeWpdx1i-XwAjSvKYKLE-iBsp1_9wwvFHk4luPWr1JjFjML0XkWOnXRqMNa1Q_aem_fqIucJO68EqHwLgEmj5Ndg</t>
+          <t>https://antonina.pr.gov.br/turismo/?categoria=1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30 19:13:24</t>
+          <t>2026-08-03 02:18:27</t>
         </is>
       </c>
     </row>
@@ -708,23 +708,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
+          <t>http://antonina.pr.gov.br/noticiasView/2263_Turma-do-3o-C-da-Escola-Municipal-Gil-Feres-realiza-aula-de-campo-e-explora-historia-e-geografia-de-Antonina.html</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30 19:13:33</t>
+          <t>2026-08-03 02:25:14</t>
         </is>
       </c>
     </row>
@@ -736,23 +736,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>http://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
+          <t>http://antonina.pr.gov.br/noticiasView/2262_Prefeitura-realiza-manutencao-das-calcadas-no-bairro-Tucunduva.html</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30 19:22:35</t>
+          <t>2026-08-03 02:25:23</t>
         </is>
       </c>
     </row>
@@ -764,23 +764,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>http://www.antonina.pr.gov.br/noticiasView/9</t>
+          <t>http://antonina.pr.gov.br/noticiasView/2261_Prefeitura-de-Antonina-instala-novos-parquinhos-nas-Escolas-Municipais-e-criancas-agora-podem-brincar-com-mais-seguranca.html</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30 19:54:21</t>
+          <t>2026-08-03 02:25:32</t>
         </is>
       </c>
     </row>
@@ -792,23 +792,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>http://www.antonina.pr.gov.br/noticiasView/e</t>
+          <t>http://antonina.pr.gov.br/noticiasView/2260_Projeto-DIMAES-realiza-oficina-em-Antonina.html</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30 19:54:30</t>
+          <t>2026-08-03 02:25:41</t>
         </is>
       </c>
     </row>
@@ -820,23 +820,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+          <t>http://antonina.pr.gov.br/noticiasView/2259_Antonina-se-prepara-para-receber-o-18o-Festival-Gospel-de-Antonina-com-o-tema-Em-Espirito-e-Verdade.html</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30 20:01:28</t>
+          <t>2026-08-03 02:25:50</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
+          <t>https://www.antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -860,11 +860,11 @@
         <v>404</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30 20:01:36</t>
+          <t>2026-08-03 02:36:35</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>http://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
+          <t>https://www.antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -888,11 +888,11 @@
         <v>404</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-30 20:02:03</t>
+          <t>2026-08-03 02:36:47</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>http://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+          <t>https://antonina.pr.gov.br/.../CHAMAMENTO-ELEICAO?fbclid=IwAR0eXNjpoLZiJ7kZYK9Ul8OJ11SelP78G2bzg5VAIIJxXN761txEOnUS8R8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -916,11 +916,11 @@
         <v>404</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-30 20:03:35</t>
+          <t>2026-08-03 02:36:48</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>http://antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
+          <t>https://antonina.pr.gov.br/.../CHAMAMENTO-ELEICAO?fbclid=IwAR0eXNjpoLZiJ7kZYK9Ul8OJ11SelP78G2bzg5VAIIJxXN761txEOnUS8R8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -944,11 +944,11 @@
         <v>404</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30 20:03:43</t>
+          <t>2026-08-03 02:37:16</t>
         </is>
       </c>
     </row>
@@ -960,23 +960,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://antonina.pr.gov.br/turismo/?categoria=1</t>
+          <t>https://www.antonina.pr.gov.br/noticiasView/e</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30 20:05:46</t>
+          <t>2026-08-03 02:37:16</t>
         </is>
       </c>
     </row>
@@ -988,23 +988,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>http://antonina.pr.gov.br/turismo/?categoria=1</t>
+          <t>http://www.antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-30 20:05:51</t>
+          <t>2026-08-03 02:44:13</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.camaramunicipaldeantonina.pr.gov.br/imprensa/noticias/0/14/0/pautas-das-sess%C3%B5es.html</t>
+          <t>http://www.antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-30 20:05:56</t>
+          <t>2026-08-03 02:44:19</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-30 20:06:00</t>
+          <t>2026-08-03 02:45:02</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/paginas-centralizadas/google.com.br</t>
+          <t>http://antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1084,11 +1084,11 @@
         <v>404</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-30 20:07:49</t>
+          <t>2026-08-03 02:51:51</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/turismo/?categoria=1</t>
+          <t>http://antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-30 20:08:33</t>
+          <t>2026-08-03 02:51:57</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/9</t>
+          <t>http://antonina.pr.gov.br/noticiasView/e</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1140,11 +1140,11 @@
         <v>404</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-30 20:23:01</t>
+          <t>2026-08-03 02:51:58</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/e</t>
+          <t>http://antonina.pr.gov.br/noticiasView/e</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1168,11 +1168,11 @@
         <v>404</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-30 20:23:10</t>
+          <t>2026-08-03 02:52:03</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
+          <t>https://antonina.pr.gov.br/uploads/pagina/arquivos/PSS-003-2025-1-1?fbclid=IwZXh0bgNhZW0CMTAAYnJpZBExNURYa1VZWllVY1k5SzFFMQEeWpdx1i-XwAjSvKYKLE-iBsp1_9wwvFHk4luPWr1JjFjML0XkWOnXRqMNa1Q_aem_fqIucJO68EqHwLgEmj5Ndg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30 20:23:35</t>
+          <t>2026-08-03 02:52:31</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/767_Mais-de-70-turistas-do-Cruzeiro-MSC-visitam-Antonina-no-ultimo-passeio-da-primeira-temporada.html</t>
+          <t>https://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E29" t="n">
         <v>6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:04</t>
+          <t>2026-08-03 02:52:36</t>
         </is>
       </c>
     </row>
@@ -1240,23 +1240,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/766_Antonina-comemora-o-Dia-Internacional-da-Mulher-com-diversas-programacoes-direcionadas-as-mulheres.html</t>
+          <t>https://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E30" t="n">
         <v>6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:10</t>
+          <t>2026-08-03 02:52:58</t>
         </is>
       </c>
     </row>
@@ -1268,23 +1268,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/765_Antonina-participa-da-Expo-Turismo-2024-.html</t>
+          <t>https://antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E31" t="n">
         <v>6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:15</t>
+          <t>2026-08-03 03:06:34</t>
         </is>
       </c>
     </row>
@@ -1296,23 +1296,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/764_Antonina-recebe-mutirao-de-limpezas-nos-manguezais-e-combate-a-dengue.html</t>
+          <t>https://antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E32" t="n">
         <v>6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:19</t>
+          <t>2026-08-03 03:06:52</t>
         </is>
       </c>
     </row>
@@ -1324,23 +1324,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/762_Prefeitura-de-Antonina-convida-a-todas-as-mulheres-a-participar-do-Projeto-Mae-T-E-A.html</t>
+          <t>https://antonina.pr.gov.br/noticiasView/e</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E33" t="n">
         <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:24</t>
+          <t>2026-08-03 03:06:53</t>
         </is>
       </c>
     </row>
@@ -1352,23 +1352,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/761_Prefeitura-de-Antonina-lanca-o-Programa-Mulher-Atual.html</t>
+          <t>https://antonina.pr.gov.br/noticiasView/e</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E34" t="n">
         <v>6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:29</t>
+          <t>2026-08-03 03:06:59</t>
         </is>
       </c>
     </row>
@@ -1380,23 +1380,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/760_Antonina-recebe-formacao-gratuita-para-quem-deseja-se-especializar-em-Turismo-de-Base-Comunitaria.html</t>
+          <t>http://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:33</t>
+          <t>2026-08-03 03:12:35</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1408,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/758_Representantes-do-Iphan-Parana-visitam-Antonina-e-discutem-pautas-importantes-sobre-o-futuro-do-Patrimonio-Historico.html</t>
+          <t>http://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:37</t>
+          <t>2026-08-03 03:12:39</t>
         </is>
       </c>
     </row>
@@ -1436,23 +1436,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/757_Antonina-recebe-cursos-de-condutor-de-cicloturismo.html</t>
+          <t>https://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:44</t>
+          <t>2026-08-03 03:17:37</t>
         </is>
       </c>
     </row>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/756_A-Prefeitura-de-Antonina-segue-realizando-acoes-em-Combate-a-Dengue.html</t>
+          <t>https://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:49</t>
+          <t>2026-08-03 03:17:44</t>
         </is>
       </c>
     </row>
@@ -1492,23 +1492,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/755_Prefeitura-de-Antonina-agradece-ao-Governo-do-Estado-pelos-mais-de-20-dias-em-apoio-ao-Combate-a-Dengue.html</t>
+          <t>http://www.antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-30 20:25:54</t>
+          <t>2026-08-03 03:44:14</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+          <t>http://www.antonina.pr.gov.br/noticiasView/9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1532,11 +1532,11 @@
         <v>404</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-30 20:28:55</t>
+          <t>2026-08-03 03:44:19</t>
         </is>
       </c>
     </row>
@@ -1548,23 +1548,723 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>http://www.antonina.pr.gov.br/noticiasView/e</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>404</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:44:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>http://www.antonina.pr.gov.br/noticiasView/e</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>404</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:44:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>404</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:45:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>404</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:46:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>https://www.antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>HTTP_404</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>404</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>404</v>
+      </c>
+      <c r="E45" t="n">
         <v>9</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-07-30 20:29:02</t>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:46:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>404</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:46:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>http://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>404</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>http://www.antonina.pr.gov.br/noticiasView/Prefeitura de Antonina segue com obras de melhoria pela cidade</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>404</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:49:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>http://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>404</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>http://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>404</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>http://antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>404</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>http://antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>404</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>404</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/noticiasView/Prefeitura de Antonina realiza evento voltado para a saúde e bem-estar das mulheres</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>404</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>404</v>
+      </c>
+      <c r="E55" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/noticiasView/13/02/2025 10:59</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>404</v>
+      </c>
+      <c r="E56" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>500</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>500</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>http://antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>500</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>http://antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>500</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>500</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>500</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>http://www.antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>500</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>http://www.antonina.pr.gov.br/turismo/?categoria=1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>500</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/uploads/pagina/arquivos/PSS-003-2025-1-1?fbclid=IwZXh0bgNhZW0CMTAAYnJpZBExNURYa1VZWllVY1k5SzFFMQEeWpdx1i-XwAjSvKYKLE-iBsp1_9wwvFHk4luPWr1JjFjML0XkWOnXRqMNa1Q_aem_fqIucJO68EqHwLgEmj5Ndg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>404</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>antonina</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://antonina.pr.gov.br/uploads/pagina/arquivos/PSS-003-2025-1-1?fbclid=IwZXh0bgNhZW0CMTAAYnJpZBExNURYa1VZWllVY1k5SzFFMQEeWpdx1i-XwAjSvKYKLE-iBsp1_9wwvFHk4luPWr1JjFjML0XkWOnXRqMNa1Q_aem_fqIucJO68EqHwLgEmj5Ndg</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>404</v>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:54:44</t>
         </is>
       </c>
     </row>
